--- a/Datos Tesis Upstream/Algoritmos y Programacion/2526-1/Participación Algoritmos 2526-1.xlsx
+++ b/Datos Tesis Upstream/Algoritmos y Programacion/2526-1/Participación Algoritmos 2526-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nelsoncarrillo/Downloads/tesis-prediccion-participacion/Datos Tesis Upstream/Algoritmos y Programacion/2526-1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{987EDF96-A0C9-2B4B-90C9-7C2DDF410328}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F70A8C8E-FC3D-A74C-B636-6A77C40DD13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="131">
   <si>
     <t>CEDULA</t>
   </si>
@@ -578,6 +578,9 @@
   <si>
     <t>miercoles</t>
   </si>
+  <si>
+    <t>carnet</t>
+  </si>
 </sst>
 </file>
 
@@ -587,7 +590,7 @@
     <numFmt numFmtId="164" formatCode="d\ mmm"/>
     <numFmt numFmtId="165" formatCode="0&quot;/20&quot;"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -666,6 +669,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -698,7 +709,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -739,23 +750,20 @@
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1136,64 +1144,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="19">
+      <c r="D1" s="18">
         <v>45908</v>
       </c>
-      <c r="E1" s="19">
+      <c r="E1" s="18">
         <v>45910</v>
       </c>
-      <c r="F1" s="19">
+      <c r="F1" s="18">
         <v>45917</v>
       </c>
-      <c r="G1" s="19">
+      <c r="G1" s="18">
         <v>45922</v>
       </c>
-      <c r="H1" s="19">
+      <c r="H1" s="18">
         <v>45924</v>
       </c>
-      <c r="I1" s="19">
+      <c r="I1" s="18">
         <v>45929</v>
       </c>
-      <c r="J1" s="20">
+      <c r="J1" s="19">
         <v>45938</v>
       </c>
-      <c r="K1" s="21">
+      <c r="K1" s="20">
         <v>45945</v>
       </c>
-      <c r="L1" s="21">
+      <c r="L1" s="20">
         <v>45952</v>
       </c>
-      <c r="M1" s="21">
+      <c r="M1" s="20">
         <v>45957</v>
       </c>
-      <c r="N1" s="21">
+      <c r="N1" s="20">
         <v>45959</v>
       </c>
-      <c r="O1" s="21">
+      <c r="O1" s="20">
         <v>45964</v>
       </c>
-      <c r="P1" s="21">
+      <c r="P1" s="20">
         <v>45971</v>
       </c>
-      <c r="Q1" s="21">
+      <c r="Q1" s="20">
         <v>45973</v>
       </c>
-      <c r="R1" s="20">
+      <c r="R1" s="19">
         <v>45978</v>
       </c>
-      <c r="S1" s="22" t="s">
+      <c r="S1" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="T1" s="22"/>
+      <c r="T1" s="21"/>
       <c r="U1" s="3"/>
       <c r="V1" s="3"/>
       <c r="W1" s="3"/>
@@ -5108,14 +5116,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AE37"/>
+  <dimension ref="A1:AF37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="4" width="16" customWidth="1"/>
-    <col min="5" max="28" width="9" customWidth="1"/>
+    <col min="1" max="5" width="16" customWidth="1"/>
+    <col min="6" max="29" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>107</v>
       </c>
@@ -5123,1595 +5131,1681 @@
         <v>126</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>108</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="16" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>109</v>
       </c>
-      <c r="B3" s="17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A5" s="16" t="s">
+      <c r="B3" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.15">
+      <c r="A5" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="F5" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16" t="s">
+      <c r="G5" s="23"/>
+      <c r="H5" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16" t="s">
+      <c r="I5" s="23"/>
+      <c r="J5" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16" t="s">
+      <c r="K5" s="23"/>
+      <c r="L5" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16" t="s">
+      <c r="M5" s="23"/>
+      <c r="N5" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="N5" s="16"/>
-      <c r="O5" s="16" t="s">
+      <c r="O5" s="23"/>
+      <c r="P5" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="16" t="s">
+      <c r="Q5" s="23"/>
+      <c r="R5" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="R5" s="16"/>
-      <c r="S5" s="16" t="s">
+      <c r="S5" s="23"/>
+      <c r="T5" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="T5" s="16"/>
-      <c r="U5" s="16" t="s">
+      <c r="U5" s="23"/>
+      <c r="V5" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="V5" s="16"/>
-      <c r="W5" s="16" t="s">
+      <c r="W5" s="23"/>
+      <c r="X5" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="X5" s="16"/>
-      <c r="Y5" s="16" t="s">
+      <c r="Y5" s="23"/>
+      <c r="Z5" s="23" t="s">
         <v>124</v>
       </c>
-      <c r="Z5" s="16"/>
-      <c r="AA5" s="16" t="s">
+      <c r="AA5" s="23"/>
+      <c r="AB5" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="AB5" s="16"/>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="17" t="s">
+      <c r="AC5" s="23"/>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.15">
+      <c r="A6" s="23"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="G6" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="H6" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="I6" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="I6" s="17" t="s">
+      <c r="J6" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="J6" s="17" t="s">
+      <c r="K6" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="K6" s="17" t="s">
+      <c r="L6" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="L6" s="17" t="s">
+      <c r="M6" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="M6" s="17" t="s">
+      <c r="N6" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="N6" s="17" t="s">
+      <c r="O6" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="O6" s="17" t="s">
+      <c r="P6" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="P6" s="17" t="s">
+      <c r="Q6" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="Q6" s="17" t="s">
+      <c r="R6" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="R6" s="17" t="s">
+      <c r="S6" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="S6" s="17" t="s">
+      <c r="T6" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="T6" s="17" t="s">
+      <c r="U6" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="U6" s="17" t="s">
+      <c r="V6" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="V6" s="17" t="s">
+      <c r="W6" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="W6" s="17" t="s">
+      <c r="X6" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="X6" s="17" t="s">
+      <c r="Y6" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="Y6" s="17" t="s">
+      <c r="Z6" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="Z6" s="17" t="s">
+      <c r="AA6" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="AA6" s="17" t="s">
+      <c r="AB6" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="AB6" s="17" t="s">
+      <c r="AC6" s="16" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A7" s="25">
-        <v>1</v>
-      </c>
-      <c r="B7" s="23" t="s">
+    <row r="7" spans="1:32" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="22">
+        <v>1</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="7">
         <v>29678921</v>
       </c>
-      <c r="E7" s="23">
-        <v>1</v>
-      </c>
-      <c r="F7" s="23"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="23">
-        <v>1</v>
-      </c>
-      <c r="I7" s="23">
-        <v>1</v>
-      </c>
-      <c r="J7" s="23">
-        <v>1</v>
-      </c>
-      <c r="K7" s="23"/>
-      <c r="L7" s="25"/>
-      <c r="M7" s="25"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="26"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="25"/>
-      <c r="R7" s="23">
-        <v>1</v>
-      </c>
-      <c r="S7" s="23"/>
-      <c r="T7" s="23">
+      <c r="E7" s="5">
+        <v>20221110498</v>
+      </c>
+      <c r="F7" s="7">
+        <v>1</v>
+      </c>
+      <c r="G7" s="7"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="7">
+        <v>1</v>
+      </c>
+      <c r="J7" s="7">
+        <v>1</v>
+      </c>
+      <c r="K7" s="7">
+        <v>1</v>
+      </c>
+      <c r="L7" s="7"/>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="22"/>
+      <c r="S7" s="7">
+        <v>1</v>
+      </c>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7">
         <v>2</v>
       </c>
-      <c r="U7" s="23"/>
-      <c r="V7" s="25"/>
-      <c r="W7" s="23"/>
-      <c r="X7" s="23">
-        <v>1</v>
-      </c>
-      <c r="Y7" s="23">
-        <v>1</v>
-      </c>
-      <c r="Z7" s="25"/>
-      <c r="AA7" s="25"/>
-      <c r="AB7" s="25"/>
-      <c r="AC7" s="25"/>
-      <c r="AD7" s="25"/>
-      <c r="AE7" s="25"/>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A8" s="25">
+      <c r="V7" s="7"/>
+      <c r="W7" s="22"/>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="7">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="22"/>
+      <c r="AB7" s="22"/>
+      <c r="AC7" s="22"/>
+      <c r="AD7" s="22"/>
+      <c r="AE7" s="22"/>
+      <c r="AF7" s="22"/>
+    </row>
+    <row r="8" spans="1:32" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8" s="22">
         <v>2</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="7">
         <v>31377471</v>
       </c>
-      <c r="E8" s="23">
-        <v>1</v>
-      </c>
-      <c r="F8" s="23"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23">
+      <c r="E8" s="5">
+        <v>20251110176</v>
+      </c>
+      <c r="F8" s="7">
+        <v>1</v>
+      </c>
+      <c r="G8" s="7"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7">
         <v>2</v>
       </c>
-      <c r="J8" s="23">
-        <v>1</v>
-      </c>
-      <c r="K8" s="23">
+      <c r="K8" s="7">
+        <v>1</v>
+      </c>
+      <c r="L8" s="7">
         <v>2</v>
       </c>
-      <c r="L8" s="25"/>
-      <c r="M8" s="25"/>
-      <c r="N8" s="24"/>
-      <c r="O8" s="26"/>
-      <c r="P8" s="23">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="25"/>
-      <c r="R8" s="23"/>
-      <c r="S8" s="23"/>
-      <c r="T8" s="23"/>
-      <c r="U8" s="23">
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="7">
+        <v>1</v>
+      </c>
+      <c r="R8" s="22"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="7">
         <v>4</v>
       </c>
-      <c r="V8" s="25"/>
-      <c r="W8" s="23">
-        <v>1</v>
-      </c>
-      <c r="X8" s="23">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="23"/>
-      <c r="Z8" s="25"/>
-      <c r="AA8" s="25"/>
-      <c r="AB8" s="25"/>
-      <c r="AC8" s="25"/>
-      <c r="AD8" s="25"/>
-      <c r="AE8" s="25"/>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A9" s="25">
+      <c r="W8" s="22"/>
+      <c r="X8" s="7">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="7"/>
+      <c r="AA8" s="22"/>
+      <c r="AB8" s="22"/>
+      <c r="AC8" s="22"/>
+      <c r="AD8" s="22"/>
+      <c r="AE8" s="22"/>
+      <c r="AF8" s="22"/>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.15">
+      <c r="A9" s="22">
         <v>3</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="7">
         <v>30906297</v>
       </c>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23">
-        <v>1</v>
-      </c>
-      <c r="G9" s="25"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23">
-        <v>1</v>
-      </c>
-      <c r="J9" s="23"/>
-      <c r="K9" s="23">
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7">
+        <v>1</v>
+      </c>
+      <c r="H9" s="22"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7">
+        <v>1</v>
+      </c>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7">
         <v>3</v>
       </c>
-      <c r="L9" s="25"/>
-      <c r="M9" s="25"/>
-      <c r="N9" s="23">
-        <v>1</v>
-      </c>
-      <c r="O9" s="26"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="25"/>
-      <c r="R9" s="23">
-        <v>1</v>
-      </c>
-      <c r="S9" s="23">
-        <v>1</v>
-      </c>
-      <c r="T9" s="23">
+      <c r="M9" s="22"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="7">
+        <v>1</v>
+      </c>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="22"/>
+      <c r="S9" s="7">
+        <v>1</v>
+      </c>
+      <c r="T9" s="7">
+        <v>1</v>
+      </c>
+      <c r="U9" s="7">
         <v>2</v>
       </c>
-      <c r="U9" s="23">
-        <v>1</v>
-      </c>
-      <c r="V9" s="25"/>
-      <c r="W9" s="23"/>
-      <c r="X9" s="23">
-        <v>1</v>
-      </c>
-      <c r="Y9" s="23">
+      <c r="V9" s="7">
+        <v>1</v>
+      </c>
+      <c r="W9" s="22"/>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="7">
         <v>3</v>
       </c>
-      <c r="Z9" s="25"/>
-      <c r="AA9" s="25"/>
-      <c r="AB9" s="25"/>
-      <c r="AC9" s="25"/>
-      <c r="AD9" s="25"/>
-      <c r="AE9" s="25"/>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A10" s="25">
+      <c r="AA9" s="22"/>
+      <c r="AB9" s="22"/>
+      <c r="AC9" s="22"/>
+      <c r="AD9" s="22"/>
+      <c r="AE9" s="22"/>
+      <c r="AF9" s="22"/>
+    </row>
+    <row r="10" spans="1:32" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10" s="22">
         <v>4</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="7">
         <v>31985434</v>
       </c>
-      <c r="E10" s="23">
-        <v>1</v>
-      </c>
-      <c r="F10" s="23"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="23"/>
-      <c r="I10" s="23"/>
-      <c r="J10" s="23"/>
-      <c r="K10" s="23"/>
-      <c r="L10" s="25"/>
-      <c r="M10" s="25"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="26"/>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="25"/>
-      <c r="R10" s="23"/>
-      <c r="S10" s="23"/>
-      <c r="T10" s="23"/>
-      <c r="U10" s="23"/>
-      <c r="V10" s="25"/>
-      <c r="W10" s="23"/>
-      <c r="X10" s="23">
-        <v>1</v>
-      </c>
-      <c r="Y10" s="23"/>
-      <c r="Z10" s="25"/>
-      <c r="AA10" s="25"/>
-      <c r="AB10" s="25"/>
-      <c r="AC10" s="25"/>
-      <c r="AD10" s="25"/>
-      <c r="AE10" s="25"/>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A11" s="25">
+      <c r="E10" s="5">
+        <v>20251110305</v>
+      </c>
+      <c r="F10" s="7">
+        <v>1</v>
+      </c>
+      <c r="G10" s="7"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="22"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
+      <c r="U10" s="7"/>
+      <c r="V10" s="7"/>
+      <c r="W10" s="22"/>
+      <c r="X10" s="7"/>
+      <c r="Y10" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="7"/>
+      <c r="AA10" s="22"/>
+      <c r="AB10" s="22"/>
+      <c r="AC10" s="22"/>
+      <c r="AD10" s="22"/>
+      <c r="AE10" s="22"/>
+      <c r="AF10" s="22"/>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.15">
+      <c r="A11" s="22">
         <v>5</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="7">
         <v>30497006</v>
       </c>
-      <c r="E11" s="23">
-        <v>1</v>
-      </c>
-      <c r="F11" s="23"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="23">
-        <v>1</v>
-      </c>
-      <c r="I11" s="23">
-        <v>1</v>
-      </c>
-      <c r="J11" s="23"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="25"/>
-      <c r="M11" s="25"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="26"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="25"/>
-      <c r="R11" s="23"/>
-      <c r="S11" s="23">
+      <c r="E11" s="7"/>
+      <c r="F11" s="7">
+        <v>1</v>
+      </c>
+      <c r="G11" s="7"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="7">
+        <v>1</v>
+      </c>
+      <c r="J11" s="7">
+        <v>1</v>
+      </c>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="22"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7">
         <v>3</v>
       </c>
-      <c r="T11" s="23"/>
-      <c r="U11" s="23"/>
-      <c r="V11" s="25"/>
-      <c r="W11" s="23"/>
-      <c r="X11" s="23">
-        <v>1</v>
-      </c>
-      <c r="Y11" s="23">
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+      <c r="W11" s="22"/>
+      <c r="X11" s="7"/>
+      <c r="Y11" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="7">
         <v>2</v>
       </c>
-      <c r="Z11" s="25"/>
-      <c r="AA11" s="25"/>
-      <c r="AB11" s="25"/>
-      <c r="AC11" s="25"/>
-      <c r="AD11" s="25"/>
-      <c r="AE11" s="25"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A12" s="25">
+      <c r="AA11" s="22"/>
+      <c r="AB11" s="22"/>
+      <c r="AC11" s="22"/>
+      <c r="AD11" s="22"/>
+      <c r="AE11" s="22"/>
+      <c r="AF11" s="22"/>
+    </row>
+    <row r="12" spans="1:32" ht="15" x14ac:dyDescent="0.2">
+      <c r="A12" s="22">
         <v>6</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="C12" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D12" s="23">
+      <c r="D12" s="7">
         <v>32535152</v>
       </c>
-      <c r="E12" s="23">
-        <v>1</v>
-      </c>
-      <c r="F12" s="23">
-        <v>1</v>
-      </c>
-      <c r="G12" s="25"/>
-      <c r="H12" s="23"/>
-      <c r="I12" s="23"/>
-      <c r="J12" s="23"/>
-      <c r="K12" s="23"/>
-      <c r="L12" s="25"/>
-      <c r="M12" s="25"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="26"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="25"/>
-      <c r="R12" s="23"/>
-      <c r="S12" s="23"/>
-      <c r="T12" s="23"/>
-      <c r="U12" s="23"/>
-      <c r="V12" s="25"/>
-      <c r="W12" s="23"/>
-      <c r="X12" s="23"/>
-      <c r="Y12" s="23"/>
-      <c r="Z12" s="25"/>
-      <c r="AA12" s="25"/>
-      <c r="AB12" s="25"/>
-      <c r="AC12" s="25"/>
-      <c r="AD12" s="25"/>
-      <c r="AE12" s="25"/>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A13" s="25">
+      <c r="E12" s="5">
+        <v>20251110436</v>
+      </c>
+      <c r="F12" s="7">
+        <v>1</v>
+      </c>
+      <c r="G12" s="7">
+        <v>1</v>
+      </c>
+      <c r="H12" s="22"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="7"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="22"/>
+      <c r="S12" s="7"/>
+      <c r="T12" s="7"/>
+      <c r="U12" s="7"/>
+      <c r="V12" s="7"/>
+      <c r="W12" s="22"/>
+      <c r="X12" s="7"/>
+      <c r="Y12" s="7"/>
+      <c r="Z12" s="7"/>
+      <c r="AA12" s="22"/>
+      <c r="AB12" s="22"/>
+      <c r="AC12" s="22"/>
+      <c r="AD12" s="22"/>
+      <c r="AE12" s="22"/>
+      <c r="AF12" s="22"/>
+    </row>
+    <row r="13" spans="1:32" ht="15" x14ac:dyDescent="0.2">
+      <c r="A13" s="22">
         <v>7</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="23">
+      <c r="D13" s="7">
         <v>30538925</v>
       </c>
-      <c r="E13" s="23">
+      <c r="E13" s="5">
+        <v>20251120012</v>
+      </c>
+      <c r="F13" s="7">
         <v>2</v>
       </c>
-      <c r="F13" s="23">
-        <v>1</v>
-      </c>
-      <c r="G13" s="25"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="23">
-        <v>1</v>
-      </c>
-      <c r="L13" s="25"/>
-      <c r="M13" s="25"/>
-      <c r="N13" s="23">
-        <v>1</v>
-      </c>
-      <c r="O13" s="26"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="25"/>
-      <c r="R13" s="23">
-        <v>1</v>
-      </c>
-      <c r="S13" s="23">
-        <v>1</v>
-      </c>
-      <c r="T13" s="23">
-        <v>1</v>
-      </c>
-      <c r="U13" s="23">
+      <c r="G13" s="7">
+        <v>1</v>
+      </c>
+      <c r="H13" s="22"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7">
+        <v>1</v>
+      </c>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="7">
+        <v>1</v>
+      </c>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="22"/>
+      <c r="S13" s="7">
+        <v>1</v>
+      </c>
+      <c r="T13" s="7">
+        <v>1</v>
+      </c>
+      <c r="U13" s="7">
+        <v>1</v>
+      </c>
+      <c r="V13" s="7">
         <v>3</v>
       </c>
-      <c r="V13" s="25"/>
-      <c r="W13" s="23"/>
-      <c r="X13" s="23"/>
-      <c r="Y13" s="23"/>
-      <c r="Z13" s="25"/>
-      <c r="AA13" s="25"/>
-      <c r="AB13" s="25"/>
-      <c r="AC13" s="25"/>
-      <c r="AD13" s="25"/>
-      <c r="AE13" s="25"/>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A14" s="25">
+      <c r="W13" s="22"/>
+      <c r="X13" s="7"/>
+      <c r="Y13" s="7"/>
+      <c r="Z13" s="7"/>
+      <c r="AA13" s="22"/>
+      <c r="AB13" s="22"/>
+      <c r="AC13" s="22"/>
+      <c r="AD13" s="22"/>
+      <c r="AE13" s="22"/>
+      <c r="AF13" s="22"/>
+    </row>
+    <row r="14" spans="1:32" ht="15" x14ac:dyDescent="0.2">
+      <c r="A14" s="22">
         <v>8</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C14" s="23" t="s">
+      <c r="C14" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="D14" s="23">
+      <c r="D14" s="7">
         <v>29947837</v>
       </c>
-      <c r="E14" s="23">
-        <v>1</v>
-      </c>
-      <c r="F14" s="23"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="23"/>
-      <c r="K14" s="23"/>
-      <c r="L14" s="25"/>
-      <c r="M14" s="25"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="26"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="25"/>
-      <c r="R14" s="23"/>
-      <c r="S14" s="23"/>
-      <c r="T14" s="23"/>
-      <c r="U14" s="23"/>
-      <c r="V14" s="25"/>
-      <c r="W14" s="23"/>
-      <c r="X14" s="23"/>
-      <c r="Y14" s="23"/>
-      <c r="Z14" s="25"/>
-      <c r="AA14" s="25"/>
-      <c r="AB14" s="25"/>
-      <c r="AC14" s="25"/>
-      <c r="AD14" s="25"/>
-      <c r="AE14" s="25"/>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A15" s="25">
+      <c r="E14" s="5">
+        <v>20201120021</v>
+      </c>
+      <c r="F14" s="7">
+        <v>1</v>
+      </c>
+      <c r="G14" s="7"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="22"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="7"/>
+      <c r="V14" s="7"/>
+      <c r="W14" s="22"/>
+      <c r="X14" s="7"/>
+      <c r="Y14" s="7"/>
+      <c r="Z14" s="7"/>
+      <c r="AA14" s="22"/>
+      <c r="AB14" s="22"/>
+      <c r="AC14" s="22"/>
+      <c r="AD14" s="22"/>
+      <c r="AE14" s="22"/>
+      <c r="AF14" s="22"/>
+    </row>
+    <row r="15" spans="1:32" ht="15" x14ac:dyDescent="0.2">
+      <c r="A15" s="22">
         <v>9</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="23" t="s">
+      <c r="C15" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="23">
+      <c r="D15" s="7">
         <v>31307883</v>
       </c>
-      <c r="E15" s="23">
-        <v>1</v>
-      </c>
-      <c r="F15" s="23">
+      <c r="E15" s="5">
+        <v>20251110060</v>
+      </c>
+      <c r="F15" s="7">
+        <v>1</v>
+      </c>
+      <c r="G15" s="7">
         <v>2</v>
       </c>
-      <c r="G15" s="25"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="23">
-        <v>1</v>
-      </c>
-      <c r="J15" s="23"/>
-      <c r="K15" s="23">
+      <c r="H15" s="22"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7">
+        <v>1</v>
+      </c>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7">
         <v>3</v>
       </c>
-      <c r="L15" s="25"/>
-      <c r="M15" s="25"/>
-      <c r="N15" s="24"/>
-      <c r="O15" s="26"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="25"/>
-      <c r="R15" s="23">
-        <v>1</v>
-      </c>
-      <c r="S15" s="23">
-        <v>1</v>
-      </c>
-      <c r="T15" s="23"/>
-      <c r="U15" s="23">
-        <v>1</v>
-      </c>
-      <c r="V15" s="25"/>
-      <c r="W15" s="23">
-        <v>1</v>
-      </c>
-      <c r="X15" s="23"/>
-      <c r="Y15" s="23">
-        <v>1</v>
-      </c>
-      <c r="Z15" s="25"/>
-      <c r="AA15" s="25"/>
-      <c r="AB15" s="25"/>
-      <c r="AC15" s="25"/>
-      <c r="AD15" s="25"/>
-      <c r="AE15" s="25"/>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A16" s="25">
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="22"/>
+      <c r="S15" s="7">
+        <v>1</v>
+      </c>
+      <c r="T15" s="7">
+        <v>1</v>
+      </c>
+      <c r="U15" s="7"/>
+      <c r="V15" s="7">
+        <v>1</v>
+      </c>
+      <c r="W15" s="22"/>
+      <c r="X15" s="7">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="7"/>
+      <c r="Z15" s="7">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="22"/>
+      <c r="AB15" s="22"/>
+      <c r="AC15" s="22"/>
+      <c r="AD15" s="22"/>
+      <c r="AE15" s="22"/>
+      <c r="AF15" s="22"/>
+    </row>
+    <row r="16" spans="1:32" ht="15" x14ac:dyDescent="0.2">
+      <c r="A16" s="22">
         <v>10</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D16" s="23">
+      <c r="D16" s="7">
         <v>31873852</v>
       </c>
-      <c r="E16" s="23">
-        <v>1</v>
-      </c>
-      <c r="F16" s="23"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="23">
-        <v>1</v>
-      </c>
-      <c r="I16" s="23"/>
-      <c r="J16" s="23"/>
-      <c r="K16" s="23">
+      <c r="E16" s="5">
+        <v>20251130018</v>
+      </c>
+      <c r="F16" s="7">
+        <v>1</v>
+      </c>
+      <c r="G16" s="7"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="7">
+        <v>1</v>
+      </c>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7">
         <v>3</v>
       </c>
-      <c r="L16" s="25"/>
-      <c r="M16" s="25"/>
-      <c r="N16" s="24"/>
-      <c r="O16" s="26"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="25"/>
-      <c r="R16" s="23"/>
-      <c r="S16" s="23"/>
-      <c r="T16" s="23"/>
-      <c r="U16" s="23"/>
-      <c r="V16" s="25"/>
-      <c r="W16" s="23"/>
-      <c r="X16" s="23"/>
-      <c r="Y16" s="23"/>
-      <c r="Z16" s="25"/>
-      <c r="AA16" s="25"/>
-      <c r="AB16" s="25"/>
-      <c r="AC16" s="25"/>
-      <c r="AD16" s="25"/>
-      <c r="AE16" s="25"/>
-    </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A17" s="25">
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="7"/>
+      <c r="R16" s="22"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="7"/>
+      <c r="U16" s="7"/>
+      <c r="V16" s="7"/>
+      <c r="W16" s="22"/>
+      <c r="X16" s="7"/>
+      <c r="Y16" s="7"/>
+      <c r="Z16" s="7"/>
+      <c r="AA16" s="22"/>
+      <c r="AB16" s="22"/>
+      <c r="AC16" s="22"/>
+      <c r="AD16" s="22"/>
+      <c r="AE16" s="22"/>
+      <c r="AF16" s="22"/>
+    </row>
+    <row r="17" spans="1:32" ht="15" x14ac:dyDescent="0.2">
+      <c r="A17" s="22">
         <v>11</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C17" s="23" t="s">
+      <c r="C17" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="23">
+      <c r="D17" s="7">
         <v>32515298</v>
       </c>
-      <c r="E17" s="23">
-        <v>1</v>
-      </c>
-      <c r="F17" s="23"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="23"/>
-      <c r="I17" s="23"/>
-      <c r="J17" s="23"/>
-      <c r="K17" s="23"/>
-      <c r="L17" s="25"/>
-      <c r="M17" s="25"/>
-      <c r="N17" s="24"/>
-      <c r="O17" s="26"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="25"/>
-      <c r="R17" s="23"/>
-      <c r="S17" s="23"/>
-      <c r="T17" s="23"/>
-      <c r="U17" s="23"/>
-      <c r="V17" s="25"/>
-      <c r="W17" s="23"/>
-      <c r="X17" s="23"/>
-      <c r="Y17" s="23"/>
-      <c r="Z17" s="25"/>
-      <c r="AA17" s="25"/>
-      <c r="AB17" s="25"/>
-      <c r="AC17" s="25"/>
-      <c r="AD17" s="25"/>
-      <c r="AE17" s="25"/>
-    </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A18" s="25">
+      <c r="E17" s="5">
+        <v>20251110065</v>
+      </c>
+      <c r="F17" s="7">
+        <v>1</v>
+      </c>
+      <c r="G17" s="7"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="22"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
+      <c r="U17" s="7"/>
+      <c r="V17" s="7"/>
+      <c r="W17" s="22"/>
+      <c r="X17" s="7"/>
+      <c r="Y17" s="7"/>
+      <c r="Z17" s="7"/>
+      <c r="AA17" s="22"/>
+      <c r="AB17" s="22"/>
+      <c r="AC17" s="22"/>
+      <c r="AD17" s="22"/>
+      <c r="AE17" s="22"/>
+      <c r="AF17" s="22"/>
+    </row>
+    <row r="18" spans="1:32" ht="15" x14ac:dyDescent="0.2">
+      <c r="A18" s="22">
         <v>12</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="C18" s="23" t="s">
+      <c r="C18" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="D18" s="23">
+      <c r="D18" s="7">
         <v>31373493</v>
       </c>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23">
-        <v>1</v>
-      </c>
-      <c r="G18" s="25"/>
-      <c r="H18" s="23"/>
-      <c r="I18" s="23"/>
-      <c r="J18" s="23"/>
-      <c r="K18" s="23"/>
-      <c r="L18" s="25"/>
-      <c r="M18" s="25"/>
-      <c r="N18" s="24"/>
-      <c r="O18" s="26"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="25"/>
-      <c r="R18" s="23"/>
-      <c r="S18" s="23"/>
-      <c r="T18" s="23"/>
-      <c r="U18" s="23"/>
-      <c r="V18" s="25"/>
-      <c r="W18" s="23"/>
-      <c r="X18" s="23"/>
-      <c r="Y18" s="23"/>
-      <c r="Z18" s="25"/>
-      <c r="AA18" s="25"/>
-      <c r="AB18" s="25"/>
-      <c r="AC18" s="25"/>
-      <c r="AD18" s="25"/>
-      <c r="AE18" s="25"/>
-    </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A19" s="25">
+      <c r="E18" s="5">
+        <v>20231120158</v>
+      </c>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7">
+        <v>1</v>
+      </c>
+      <c r="H18" s="22"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="7"/>
+      <c r="R18" s="22"/>
+      <c r="S18" s="7"/>
+      <c r="T18" s="7"/>
+      <c r="U18" s="7"/>
+      <c r="V18" s="7"/>
+      <c r="W18" s="22"/>
+      <c r="X18" s="7"/>
+      <c r="Y18" s="7"/>
+      <c r="Z18" s="7"/>
+      <c r="AA18" s="22"/>
+      <c r="AB18" s="22"/>
+      <c r="AC18" s="22"/>
+      <c r="AD18" s="22"/>
+      <c r="AE18" s="22"/>
+      <c r="AF18" s="22"/>
+    </row>
+    <row r="19" spans="1:32" ht="15" x14ac:dyDescent="0.2">
+      <c r="A19" s="22">
         <v>13</v>
       </c>
-      <c r="B19" s="23" t="s">
+      <c r="B19" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C19" s="23" t="s">
+      <c r="C19" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D19" s="23">
+      <c r="D19" s="7">
         <v>32347981</v>
       </c>
-      <c r="E19" s="23">
-        <v>1</v>
-      </c>
-      <c r="F19" s="23"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="23"/>
-      <c r="I19" s="23"/>
-      <c r="J19" s="23"/>
-      <c r="K19" s="23"/>
-      <c r="L19" s="25"/>
-      <c r="M19" s="25"/>
-      <c r="N19" s="24"/>
-      <c r="O19" s="26"/>
-      <c r="P19" s="23"/>
-      <c r="Q19" s="25"/>
-      <c r="R19" s="23"/>
-      <c r="S19" s="23"/>
-      <c r="T19" s="23"/>
-      <c r="U19" s="23"/>
-      <c r="V19" s="25"/>
-      <c r="W19" s="23"/>
-      <c r="X19" s="23"/>
-      <c r="Y19" s="23"/>
-      <c r="Z19" s="25"/>
-      <c r="AA19" s="25"/>
-      <c r="AB19" s="25"/>
-      <c r="AC19" s="25"/>
-      <c r="AD19" s="25"/>
-      <c r="AE19" s="25"/>
-    </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A20" s="25">
+      <c r="E19" s="5">
+        <v>20251110214</v>
+      </c>
+      <c r="F19" s="7">
+        <v>1</v>
+      </c>
+      <c r="G19" s="7"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="22"/>
+      <c r="N19" s="22"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="22"/>
+      <c r="Q19" s="7"/>
+      <c r="R19" s="22"/>
+      <c r="S19" s="7"/>
+      <c r="T19" s="7"/>
+      <c r="U19" s="7"/>
+      <c r="V19" s="7"/>
+      <c r="W19" s="22"/>
+      <c r="X19" s="7"/>
+      <c r="Y19" s="7"/>
+      <c r="Z19" s="7"/>
+      <c r="AA19" s="22"/>
+      <c r="AB19" s="22"/>
+      <c r="AC19" s="22"/>
+      <c r="AD19" s="22"/>
+      <c r="AE19" s="22"/>
+      <c r="AF19" s="22"/>
+    </row>
+    <row r="20" spans="1:32" ht="15" x14ac:dyDescent="0.2">
+      <c r="A20" s="22">
         <v>14</v>
       </c>
-      <c r="B20" s="23" t="s">
+      <c r="B20" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D20" s="23">
+      <c r="D20" s="7">
         <v>32502105</v>
       </c>
-      <c r="E20" s="23">
-        <v>1</v>
-      </c>
-      <c r="F20" s="23"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="23"/>
-      <c r="I20" s="23"/>
-      <c r="J20" s="23"/>
-      <c r="K20" s="23"/>
-      <c r="L20" s="25"/>
-      <c r="M20" s="25"/>
-      <c r="N20" s="24"/>
-      <c r="O20" s="26"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="25"/>
-      <c r="R20" s="23"/>
-      <c r="S20" s="23">
+      <c r="E20" s="5">
+        <v>20251120137</v>
+      </c>
+      <c r="F20" s="7">
+        <v>1</v>
+      </c>
+      <c r="G20" s="7"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="7"/>
+      <c r="R20" s="22"/>
+      <c r="S20" s="7"/>
+      <c r="T20" s="7">
         <v>2</v>
       </c>
-      <c r="T20" s="23"/>
-      <c r="U20" s="23"/>
-      <c r="V20" s="25"/>
-      <c r="W20" s="23">
+      <c r="U20" s="7"/>
+      <c r="V20" s="7"/>
+      <c r="W20" s="22"/>
+      <c r="X20" s="7">
         <v>3</v>
       </c>
-      <c r="X20" s="23">
+      <c r="Y20" s="7">
         <v>2</v>
       </c>
-      <c r="Y20" s="23"/>
-      <c r="Z20" s="25"/>
-      <c r="AA20" s="25"/>
-      <c r="AB20" s="25"/>
-      <c r="AC20" s="25"/>
-      <c r="AD20" s="25"/>
-      <c r="AE20" s="25"/>
-    </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A21" s="25">
+      <c r="Z20" s="7"/>
+      <c r="AA20" s="22"/>
+      <c r="AB20" s="22"/>
+      <c r="AC20" s="22"/>
+      <c r="AD20" s="22"/>
+      <c r="AE20" s="22"/>
+      <c r="AF20" s="22"/>
+    </row>
+    <row r="21" spans="1:32" ht="15" x14ac:dyDescent="0.2">
+      <c r="A21" s="22">
         <v>15</v>
       </c>
-      <c r="B21" s="23" t="s">
+      <c r="B21" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="C21" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D21" s="23">
+      <c r="D21" s="7">
         <v>28318117</v>
       </c>
-      <c r="E21" s="23">
-        <v>1</v>
-      </c>
-      <c r="F21" s="23"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="23"/>
-      <c r="J21" s="23"/>
-      <c r="K21" s="23"/>
-      <c r="L21" s="25"/>
-      <c r="M21" s="25"/>
-      <c r="N21" s="24"/>
-      <c r="O21" s="26"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="25"/>
-      <c r="R21" s="23"/>
-      <c r="S21" s="23"/>
-      <c r="T21" s="23"/>
-      <c r="U21" s="23"/>
-      <c r="V21" s="25"/>
-      <c r="W21" s="23"/>
-      <c r="X21" s="23"/>
-      <c r="Y21" s="23">
-        <v>1</v>
-      </c>
-      <c r="Z21" s="25"/>
-      <c r="AA21" s="25"/>
-      <c r="AB21" s="25"/>
-      <c r="AC21" s="25"/>
-      <c r="AD21" s="25"/>
-      <c r="AE21" s="25"/>
-    </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A22" s="25">
+      <c r="E21" s="5">
+        <v>20211110543</v>
+      </c>
+      <c r="F21" s="7">
+        <v>1</v>
+      </c>
+      <c r="G21" s="7"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="22"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="22"/>
+      <c r="Q21" s="7"/>
+      <c r="R21" s="22"/>
+      <c r="S21" s="7"/>
+      <c r="T21" s="7"/>
+      <c r="U21" s="7"/>
+      <c r="V21" s="7"/>
+      <c r="W21" s="22"/>
+      <c r="X21" s="7"/>
+      <c r="Y21" s="7"/>
+      <c r="Z21" s="7">
+        <v>1</v>
+      </c>
+      <c r="AA21" s="22"/>
+      <c r="AB21" s="22"/>
+      <c r="AC21" s="22"/>
+      <c r="AD21" s="22"/>
+      <c r="AE21" s="22"/>
+      <c r="AF21" s="22"/>
+    </row>
+    <row r="22" spans="1:32" ht="15" x14ac:dyDescent="0.2">
+      <c r="A22" s="22">
         <v>16</v>
       </c>
-      <c r="B22" s="23" t="s">
+      <c r="B22" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="C22" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="D22" s="23">
+      <c r="D22" s="7">
         <v>30346514</v>
       </c>
-      <c r="E22" s="23">
-        <v>1</v>
-      </c>
-      <c r="F22" s="23"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="23">
-        <v>1</v>
-      </c>
-      <c r="J22" s="23">
-        <v>1</v>
-      </c>
-      <c r="K22" s="23"/>
-      <c r="L22" s="25"/>
-      <c r="M22" s="25"/>
-      <c r="N22" s="24"/>
-      <c r="O22" s="26"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="25"/>
-      <c r="R22" s="23"/>
-      <c r="S22" s="23"/>
-      <c r="T22" s="23"/>
-      <c r="U22" s="23"/>
-      <c r="V22" s="25"/>
-      <c r="W22" s="23"/>
-      <c r="X22" s="23"/>
-      <c r="Y22" s="23">
-        <v>1</v>
-      </c>
-      <c r="Z22" s="25"/>
-      <c r="AA22" s="25"/>
-      <c r="AB22" s="25"/>
-      <c r="AC22" s="25"/>
-      <c r="AD22" s="25"/>
-      <c r="AE22" s="25"/>
-    </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A23" s="25">
+      <c r="E22" s="5">
+        <v>20231110814</v>
+      </c>
+      <c r="F22" s="7">
+        <v>1</v>
+      </c>
+      <c r="G22" s="7"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7">
+        <v>1</v>
+      </c>
+      <c r="K22" s="7">
+        <v>1</v>
+      </c>
+      <c r="L22" s="7"/>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="22"/>
+      <c r="Q22" s="7"/>
+      <c r="R22" s="22"/>
+      <c r="S22" s="7"/>
+      <c r="T22" s="7"/>
+      <c r="U22" s="7"/>
+      <c r="V22" s="7"/>
+      <c r="W22" s="22"/>
+      <c r="X22" s="7"/>
+      <c r="Y22" s="7"/>
+      <c r="Z22" s="7">
+        <v>1</v>
+      </c>
+      <c r="AA22" s="22"/>
+      <c r="AB22" s="22"/>
+      <c r="AC22" s="22"/>
+      <c r="AD22" s="22"/>
+      <c r="AE22" s="22"/>
+      <c r="AF22" s="22"/>
+    </row>
+    <row r="23" spans="1:32" ht="15" x14ac:dyDescent="0.2">
+      <c r="A23" s="22">
         <v>17</v>
       </c>
-      <c r="B23" s="23" t="s">
+      <c r="B23" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C23" s="23" t="s">
+      <c r="C23" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D23" s="23">
+      <c r="D23" s="7">
         <v>32124905</v>
       </c>
-      <c r="E23" s="23">
-        <v>1</v>
-      </c>
-      <c r="F23" s="23"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="23"/>
-      <c r="K23" s="23"/>
-      <c r="L23" s="25"/>
-      <c r="M23" s="25"/>
-      <c r="N23" s="24"/>
-      <c r="O23" s="26"/>
-      <c r="P23" s="23"/>
-      <c r="Q23" s="25"/>
-      <c r="R23" s="23"/>
-      <c r="S23" s="23"/>
-      <c r="T23" s="23"/>
-      <c r="U23" s="23"/>
-      <c r="V23" s="25"/>
-      <c r="W23" s="23"/>
-      <c r="X23" s="23"/>
-      <c r="Y23" s="23"/>
-      <c r="Z23" s="25"/>
-      <c r="AA23" s="25"/>
-      <c r="AB23" s="25"/>
-      <c r="AC23" s="25"/>
-      <c r="AD23" s="25"/>
-      <c r="AE23" s="25"/>
-    </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A24" s="25">
+      <c r="E23" s="5">
+        <v>20251130008</v>
+      </c>
+      <c r="F23" s="7">
+        <v>1</v>
+      </c>
+      <c r="G23" s="7"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="22"/>
+      <c r="Q23" s="7"/>
+      <c r="R23" s="22"/>
+      <c r="S23" s="7"/>
+      <c r="T23" s="7"/>
+      <c r="U23" s="7"/>
+      <c r="V23" s="7"/>
+      <c r="W23" s="22"/>
+      <c r="X23" s="7"/>
+      <c r="Y23" s="7"/>
+      <c r="Z23" s="7"/>
+      <c r="AA23" s="22"/>
+      <c r="AB23" s="22"/>
+      <c r="AC23" s="22"/>
+      <c r="AD23" s="22"/>
+      <c r="AE23" s="22"/>
+      <c r="AF23" s="22"/>
+    </row>
+    <row r="24" spans="1:32" ht="15" x14ac:dyDescent="0.2">
+      <c r="A24" s="22">
         <v>18</v>
       </c>
-      <c r="B24" s="23" t="s">
+      <c r="B24" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C24" s="23" t="s">
+      <c r="C24" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D24" s="23">
+      <c r="D24" s="7">
         <v>32397222</v>
       </c>
-      <c r="E24" s="23">
-        <v>1</v>
-      </c>
-      <c r="F24" s="23">
-        <v>1</v>
-      </c>
-      <c r="G24" s="25"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
-      <c r="J24" s="23"/>
-      <c r="K24" s="23"/>
-      <c r="L24" s="25"/>
-      <c r="M24" s="25"/>
-      <c r="N24" s="24"/>
-      <c r="O24" s="26"/>
-      <c r="P24" s="23"/>
-      <c r="Q24" s="25"/>
-      <c r="R24" s="23"/>
-      <c r="S24" s="23"/>
-      <c r="T24" s="23"/>
-      <c r="U24" s="23"/>
-      <c r="V24" s="25"/>
-      <c r="W24" s="23"/>
-      <c r="X24" s="23"/>
-      <c r="Y24" s="23"/>
-      <c r="Z24" s="25"/>
-      <c r="AA24" s="25"/>
-      <c r="AB24" s="25"/>
-      <c r="AC24" s="25"/>
-      <c r="AD24" s="25"/>
-      <c r="AE24" s="25"/>
-    </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A25" s="25">
+      <c r="E24" s="5">
+        <v>20251110310</v>
+      </c>
+      <c r="F24" s="7">
+        <v>1</v>
+      </c>
+      <c r="G24" s="7">
+        <v>1</v>
+      </c>
+      <c r="H24" s="22"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="22"/>
+      <c r="N24" s="22"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="22"/>
+      <c r="Q24" s="7"/>
+      <c r="R24" s="22"/>
+      <c r="S24" s="7"/>
+      <c r="T24" s="7"/>
+      <c r="U24" s="7"/>
+      <c r="V24" s="7"/>
+      <c r="W24" s="22"/>
+      <c r="X24" s="7"/>
+      <c r="Y24" s="7"/>
+      <c r="Z24" s="7"/>
+      <c r="AA24" s="22"/>
+      <c r="AB24" s="22"/>
+      <c r="AC24" s="22"/>
+      <c r="AD24" s="22"/>
+      <c r="AE24" s="22"/>
+      <c r="AF24" s="22"/>
+    </row>
+    <row r="25" spans="1:32" ht="15" x14ac:dyDescent="0.2">
+      <c r="A25" s="22">
         <v>19</v>
       </c>
-      <c r="B25" s="23" t="s">
+      <c r="B25" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="C25" s="23" t="s">
+      <c r="C25" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="D25" s="23">
+      <c r="D25" s="7">
         <v>30156914</v>
       </c>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="23"/>
-      <c r="K25" s="23"/>
-      <c r="L25" s="25"/>
-      <c r="M25" s="25"/>
-      <c r="N25" s="24"/>
-      <c r="O25" s="26"/>
-      <c r="P25" s="23"/>
-      <c r="Q25" s="25"/>
-      <c r="R25" s="23"/>
-      <c r="S25" s="23"/>
-      <c r="T25" s="23"/>
-      <c r="U25" s="23"/>
-      <c r="V25" s="25"/>
-      <c r="W25" s="23"/>
-      <c r="X25" s="23"/>
-      <c r="Y25" s="23"/>
-      <c r="Z25" s="25"/>
-      <c r="AA25" s="25"/>
-      <c r="AB25" s="25"/>
-      <c r="AC25" s="25"/>
-      <c r="AD25" s="25"/>
-      <c r="AE25" s="25"/>
-    </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A26" s="25">
-        <v>20</v>
-      </c>
-      <c r="B26" s="23" t="s">
+      <c r="E25" s="5">
+        <v>20211120116</v>
+      </c>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="22"/>
+      <c r="N25" s="22"/>
+      <c r="O25" s="8"/>
+      <c r="P25" s="22"/>
+      <c r="Q25" s="7"/>
+      <c r="R25" s="22"/>
+      <c r="S25" s="7"/>
+      <c r="T25" s="7"/>
+      <c r="U25" s="7"/>
+      <c r="V25" s="7"/>
+      <c r="W25" s="22"/>
+      <c r="X25" s="7"/>
+      <c r="Y25" s="7"/>
+      <c r="Z25" s="7"/>
+      <c r="AA25" s="22"/>
+      <c r="AB25" s="22"/>
+      <c r="AC25" s="22"/>
+      <c r="AD25" s="22"/>
+      <c r="AE25" s="22"/>
+      <c r="AF25" s="22"/>
+    </row>
+    <row r="26" spans="1:32" ht="15" x14ac:dyDescent="0.2">
+      <c r="A26" s="22">
+        <v>20</v>
+      </c>
+      <c r="B26" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C26" s="23" t="s">
+      <c r="C26" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="D26" s="23">
+      <c r="D26" s="7">
         <v>32333927</v>
       </c>
-      <c r="E26" s="23">
-        <v>1</v>
-      </c>
-      <c r="F26" s="23">
+      <c r="E26" s="5">
+        <v>20251120107</v>
+      </c>
+      <c r="F26" s="7">
+        <v>1</v>
+      </c>
+      <c r="G26" s="7">
         <v>2</v>
       </c>
-      <c r="G26" s="25"/>
-      <c r="H26" s="23"/>
-      <c r="I26" s="23">
+      <c r="H26" s="22"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7">
         <v>2</v>
       </c>
-      <c r="J26" s="23"/>
-      <c r="K26" s="23"/>
-      <c r="L26" s="25"/>
-      <c r="M26" s="25"/>
-      <c r="N26" s="24"/>
-      <c r="O26" s="26"/>
-      <c r="P26" s="23"/>
-      <c r="Q26" s="25"/>
-      <c r="R26" s="23"/>
-      <c r="S26" s="23"/>
-      <c r="T26" s="23"/>
-      <c r="U26" s="23"/>
-      <c r="V26" s="25"/>
-      <c r="W26" s="23">
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
+      <c r="M26" s="22"/>
+      <c r="N26" s="22"/>
+      <c r="O26" s="8"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="7"/>
+      <c r="R26" s="22"/>
+      <c r="S26" s="7"/>
+      <c r="T26" s="7"/>
+      <c r="U26" s="7"/>
+      <c r="V26" s="7"/>
+      <c r="W26" s="22"/>
+      <c r="X26" s="7">
         <v>3</v>
       </c>
-      <c r="X26" s="23">
+      <c r="Y26" s="7">
         <v>2</v>
       </c>
-      <c r="Y26" s="23"/>
-      <c r="Z26" s="25"/>
-      <c r="AA26" s="25"/>
-      <c r="AB26" s="25"/>
-      <c r="AC26" s="25"/>
-      <c r="AD26" s="25"/>
-      <c r="AE26" s="25"/>
-    </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A27" s="25">
+      <c r="Z26" s="7"/>
+      <c r="AA26" s="22"/>
+      <c r="AB26" s="22"/>
+      <c r="AC26" s="22"/>
+      <c r="AD26" s="22"/>
+      <c r="AE26" s="22"/>
+      <c r="AF26" s="22"/>
+    </row>
+    <row r="27" spans="1:32" ht="15" x14ac:dyDescent="0.2">
+      <c r="A27" s="22">
         <v>21</v>
       </c>
-      <c r="B27" s="23" t="s">
+      <c r="B27" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="C27" s="23" t="s">
+      <c r="C27" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D27" s="23">
+      <c r="D27" s="7">
         <v>27714378</v>
       </c>
-      <c r="E27" s="23">
-        <v>1</v>
-      </c>
-      <c r="F27" s="23"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="23"/>
-      <c r="I27" s="23"/>
-      <c r="J27" s="23"/>
-      <c r="K27" s="23"/>
-      <c r="L27" s="25"/>
-      <c r="M27" s="25"/>
-      <c r="N27" s="24"/>
-      <c r="O27" s="26"/>
-      <c r="P27" s="23"/>
-      <c r="Q27" s="25"/>
-      <c r="R27" s="23"/>
-      <c r="S27" s="23"/>
-      <c r="T27" s="23"/>
-      <c r="U27" s="23"/>
-      <c r="V27" s="25"/>
-      <c r="W27" s="23"/>
-      <c r="X27" s="23"/>
-      <c r="Y27" s="23"/>
-      <c r="Z27" s="25"/>
-      <c r="AA27" s="25"/>
-      <c r="AB27" s="25"/>
-      <c r="AC27" s="25"/>
-      <c r="AD27" s="25"/>
-      <c r="AE27" s="25"/>
-    </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A28" s="25">
+      <c r="E27" s="5">
+        <v>20251110216</v>
+      </c>
+      <c r="F27" s="7">
+        <v>1</v>
+      </c>
+      <c r="G27" s="7"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+      <c r="M27" s="22"/>
+      <c r="N27" s="22"/>
+      <c r="O27" s="8"/>
+      <c r="P27" s="22"/>
+      <c r="Q27" s="7"/>
+      <c r="R27" s="22"/>
+      <c r="S27" s="7"/>
+      <c r="T27" s="7"/>
+      <c r="U27" s="7"/>
+      <c r="V27" s="7"/>
+      <c r="W27" s="22"/>
+      <c r="X27" s="7"/>
+      <c r="Y27" s="7"/>
+      <c r="Z27" s="7"/>
+      <c r="AA27" s="22"/>
+      <c r="AB27" s="22"/>
+      <c r="AC27" s="22"/>
+      <c r="AD27" s="22"/>
+      <c r="AE27" s="22"/>
+      <c r="AF27" s="22"/>
+    </row>
+    <row r="28" spans="1:32" ht="15" x14ac:dyDescent="0.2">
+      <c r="A28" s="22">
         <v>22</v>
       </c>
-      <c r="B28" s="23" t="s">
+      <c r="B28" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C28" s="23" t="s">
+      <c r="C28" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="D28" s="23">
+      <c r="D28" s="7">
         <v>29662246</v>
       </c>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="25"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23"/>
-      <c r="J28" s="23"/>
-      <c r="K28" s="23"/>
-      <c r="L28" s="25"/>
-      <c r="M28" s="25"/>
-      <c r="N28" s="24"/>
-      <c r="O28" s="26"/>
-      <c r="P28" s="23"/>
-      <c r="Q28" s="25"/>
-      <c r="R28" s="23"/>
-      <c r="S28" s="23"/>
-      <c r="T28" s="23"/>
-      <c r="U28" s="23"/>
-      <c r="V28" s="25"/>
-      <c r="W28" s="23"/>
-      <c r="X28" s="23"/>
-      <c r="Y28" s="23"/>
-      <c r="Z28" s="25"/>
-      <c r="AA28" s="25"/>
-      <c r="AB28" s="25"/>
-      <c r="AC28" s="25"/>
-      <c r="AD28" s="25"/>
-      <c r="AE28" s="25"/>
-    </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A29" s="25">
+      <c r="E28" s="5">
+        <v>20201120176</v>
+      </c>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="7"/>
+      <c r="L28" s="7"/>
+      <c r="M28" s="22"/>
+      <c r="N28" s="22"/>
+      <c r="O28" s="8"/>
+      <c r="P28" s="22"/>
+      <c r="Q28" s="7"/>
+      <c r="R28" s="22"/>
+      <c r="S28" s="7"/>
+      <c r="T28" s="7"/>
+      <c r="U28" s="7"/>
+      <c r="V28" s="7"/>
+      <c r="W28" s="22"/>
+      <c r="X28" s="7"/>
+      <c r="Y28" s="7"/>
+      <c r="Z28" s="7"/>
+      <c r="AA28" s="22"/>
+      <c r="AB28" s="22"/>
+      <c r="AC28" s="22"/>
+      <c r="AD28" s="22"/>
+      <c r="AE28" s="22"/>
+      <c r="AF28" s="22"/>
+    </row>
+    <row r="29" spans="1:32" ht="15" x14ac:dyDescent="0.2">
+      <c r="A29" s="22">
         <v>23</v>
       </c>
-      <c r="B29" s="23" t="s">
+      <c r="B29" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="C29" s="23" t="s">
+      <c r="C29" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="D29" s="23">
+      <c r="D29" s="7">
         <v>31623260</v>
       </c>
-      <c r="E29" s="23">
-        <v>1</v>
-      </c>
-      <c r="F29" s="23">
-        <v>1</v>
-      </c>
-      <c r="G29" s="25"/>
-      <c r="H29" s="23"/>
-      <c r="I29" s="23">
+      <c r="E29" s="5">
+        <v>20241110106</v>
+      </c>
+      <c r="F29" s="7">
+        <v>1</v>
+      </c>
+      <c r="G29" s="7">
+        <v>1</v>
+      </c>
+      <c r="H29" s="22"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7">
         <v>2</v>
       </c>
-      <c r="J29" s="23">
-        <v>1</v>
-      </c>
-      <c r="K29" s="23"/>
-      <c r="L29" s="25"/>
-      <c r="M29" s="25"/>
-      <c r="N29" s="24"/>
-      <c r="O29" s="26"/>
-      <c r="P29" s="23"/>
-      <c r="Q29" s="25"/>
-      <c r="R29" s="23">
-        <v>1</v>
-      </c>
-      <c r="S29" s="23"/>
-      <c r="T29" s="23"/>
-      <c r="U29" s="23"/>
-      <c r="V29" s="25"/>
-      <c r="W29" s="23"/>
-      <c r="X29" s="23"/>
-      <c r="Y29" s="23">
-        <v>1</v>
-      </c>
-      <c r="Z29" s="25"/>
-      <c r="AA29" s="25"/>
-      <c r="AB29" s="25"/>
-      <c r="AC29" s="25"/>
-      <c r="AD29" s="25"/>
-      <c r="AE29" s="25"/>
-    </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A30" s="25">
+      <c r="K29" s="7">
+        <v>1</v>
+      </c>
+      <c r="L29" s="7"/>
+      <c r="M29" s="22"/>
+      <c r="N29" s="22"/>
+      <c r="O29" s="8"/>
+      <c r="P29" s="22"/>
+      <c r="Q29" s="7"/>
+      <c r="R29" s="22"/>
+      <c r="S29" s="7">
+        <v>1</v>
+      </c>
+      <c r="T29" s="7"/>
+      <c r="U29" s="7"/>
+      <c r="V29" s="7"/>
+      <c r="W29" s="22"/>
+      <c r="X29" s="7"/>
+      <c r="Y29" s="7"/>
+      <c r="Z29" s="7">
+        <v>1</v>
+      </c>
+      <c r="AA29" s="22"/>
+      <c r="AB29" s="22"/>
+      <c r="AC29" s="22"/>
+      <c r="AD29" s="22"/>
+      <c r="AE29" s="22"/>
+      <c r="AF29" s="22"/>
+    </row>
+    <row r="30" spans="1:32" ht="15" x14ac:dyDescent="0.2">
+      <c r="A30" s="22">
         <v>24</v>
       </c>
-      <c r="B30" s="23" t="s">
+      <c r="B30" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C30" s="23" t="s">
+      <c r="C30" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="D30" s="23">
+      <c r="D30" s="7">
         <v>32080790</v>
       </c>
-      <c r="E30" s="23">
-        <v>1</v>
-      </c>
-      <c r="F30" s="23"/>
-      <c r="G30" s="25"/>
-      <c r="H30" s="23"/>
-      <c r="I30" s="23"/>
-      <c r="J30" s="23"/>
-      <c r="K30" s="23"/>
-      <c r="L30" s="25"/>
-      <c r="M30" s="25"/>
-      <c r="N30" s="24"/>
-      <c r="O30" s="26"/>
-      <c r="P30" s="23"/>
-      <c r="Q30" s="25"/>
-      <c r="R30" s="23"/>
-      <c r="S30" s="23"/>
-      <c r="T30" s="23"/>
-      <c r="U30" s="23"/>
-      <c r="V30" s="25"/>
-      <c r="W30" s="23"/>
-      <c r="X30" s="23"/>
-      <c r="Y30" s="23"/>
-      <c r="Z30" s="25"/>
-      <c r="AA30" s="25"/>
-      <c r="AB30" s="25"/>
-      <c r="AC30" s="25"/>
-      <c r="AD30" s="25"/>
-      <c r="AE30" s="25"/>
-    </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A31" s="25">
+      <c r="E30" s="5">
+        <v>20251130147</v>
+      </c>
+      <c r="F30" s="7">
+        <v>1</v>
+      </c>
+      <c r="G30" s="7"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="7"/>
+      <c r="K30" s="7"/>
+      <c r="L30" s="7"/>
+      <c r="M30" s="22"/>
+      <c r="N30" s="22"/>
+      <c r="O30" s="8"/>
+      <c r="P30" s="22"/>
+      <c r="Q30" s="7"/>
+      <c r="R30" s="22"/>
+      <c r="S30" s="7"/>
+      <c r="T30" s="7"/>
+      <c r="U30" s="7"/>
+      <c r="V30" s="7"/>
+      <c r="W30" s="22"/>
+      <c r="X30" s="7"/>
+      <c r="Y30" s="7"/>
+      <c r="Z30" s="7"/>
+      <c r="AA30" s="22"/>
+      <c r="AB30" s="22"/>
+      <c r="AC30" s="22"/>
+      <c r="AD30" s="22"/>
+      <c r="AE30" s="22"/>
+      <c r="AF30" s="22"/>
+    </row>
+    <row r="31" spans="1:32" ht="15" x14ac:dyDescent="0.2">
+      <c r="A31" s="22">
         <v>25</v>
       </c>
-      <c r="B31" s="23" t="s">
+      <c r="B31" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C31" s="23" t="s">
+      <c r="C31" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D31" s="23">
+      <c r="D31" s="7">
         <v>29678946</v>
       </c>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="25"/>
-      <c r="H31" s="23"/>
-      <c r="I31" s="23"/>
-      <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="25"/>
-      <c r="M31" s="25"/>
-      <c r="N31" s="24"/>
-      <c r="O31" s="26"/>
-      <c r="P31" s="23"/>
-      <c r="Q31" s="25"/>
-      <c r="R31" s="23"/>
-      <c r="S31" s="23"/>
-      <c r="T31" s="23"/>
-      <c r="U31" s="23"/>
-      <c r="V31" s="25"/>
-      <c r="W31" s="23"/>
-      <c r="X31" s="23"/>
-      <c r="Y31" s="23"/>
-      <c r="Z31" s="25"/>
-      <c r="AA31" s="25"/>
-      <c r="AB31" s="25"/>
-      <c r="AC31" s="25"/>
-      <c r="AD31" s="25"/>
-      <c r="AE31" s="25"/>
-    </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A32" s="25">
+      <c r="E31" s="5">
+        <v>20231110776</v>
+      </c>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
+      <c r="K31" s="7"/>
+      <c r="L31" s="7"/>
+      <c r="M31" s="22"/>
+      <c r="N31" s="22"/>
+      <c r="O31" s="8"/>
+      <c r="P31" s="22"/>
+      <c r="Q31" s="7"/>
+      <c r="R31" s="22"/>
+      <c r="S31" s="7"/>
+      <c r="T31" s="7"/>
+      <c r="U31" s="7"/>
+      <c r="V31" s="7"/>
+      <c r="W31" s="22"/>
+      <c r="X31" s="7"/>
+      <c r="Y31" s="7"/>
+      <c r="Z31" s="7"/>
+      <c r="AA31" s="22"/>
+      <c r="AB31" s="22"/>
+      <c r="AC31" s="22"/>
+      <c r="AD31" s="22"/>
+      <c r="AE31" s="22"/>
+      <c r="AF31" s="22"/>
+    </row>
+    <row r="32" spans="1:32" ht="15" x14ac:dyDescent="0.2">
+      <c r="A32" s="22">
         <v>26</v>
       </c>
-      <c r="B32" s="23" t="s">
+      <c r="B32" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="C32" s="23" t="s">
+      <c r="C32" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="D32" s="23">
+      <c r="D32" s="7">
         <v>34202891</v>
       </c>
-      <c r="E32" s="23">
-        <v>1</v>
-      </c>
-      <c r="F32" s="23"/>
-      <c r="G32" s="25"/>
-      <c r="H32" s="23"/>
-      <c r="I32" s="23"/>
-      <c r="J32" s="23"/>
-      <c r="K32" s="23"/>
-      <c r="L32" s="25"/>
-      <c r="M32" s="25"/>
-      <c r="N32" s="24"/>
-      <c r="O32" s="26"/>
-      <c r="P32" s="23"/>
-      <c r="Q32" s="25"/>
-      <c r="R32" s="23"/>
-      <c r="S32" s="23"/>
-      <c r="T32" s="23"/>
-      <c r="U32" s="23"/>
-      <c r="V32" s="25"/>
-      <c r="W32" s="23"/>
-      <c r="X32" s="23"/>
-      <c r="Y32" s="23"/>
-      <c r="Z32" s="25"/>
-      <c r="AA32" s="25"/>
-      <c r="AB32" s="25"/>
-      <c r="AC32" s="25"/>
-      <c r="AD32" s="25"/>
-      <c r="AE32" s="25"/>
-    </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A33" s="25">
+      <c r="E32" s="5">
+        <v>20251110215</v>
+      </c>
+      <c r="F32" s="7">
+        <v>1</v>
+      </c>
+      <c r="G32" s="7"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="7"/>
+      <c r="K32" s="7"/>
+      <c r="L32" s="7"/>
+      <c r="M32" s="22"/>
+      <c r="N32" s="22"/>
+      <c r="O32" s="8"/>
+      <c r="P32" s="22"/>
+      <c r="Q32" s="7"/>
+      <c r="R32" s="22"/>
+      <c r="S32" s="7"/>
+      <c r="T32" s="7"/>
+      <c r="U32" s="7"/>
+      <c r="V32" s="7"/>
+      <c r="W32" s="22"/>
+      <c r="X32" s="7"/>
+      <c r="Y32" s="7"/>
+      <c r="Z32" s="7"/>
+      <c r="AA32" s="22"/>
+      <c r="AB32" s="22"/>
+      <c r="AC32" s="22"/>
+      <c r="AD32" s="22"/>
+      <c r="AE32" s="22"/>
+      <c r="AF32" s="22"/>
+    </row>
+    <row r="33" spans="1:32" ht="15" x14ac:dyDescent="0.2">
+      <c r="A33" s="22">
         <v>27</v>
       </c>
-      <c r="B33" s="23" t="s">
+      <c r="B33" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C33" s="23" t="s">
+      <c r="C33" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="D33" s="23">
+      <c r="D33" s="7">
         <v>31707262</v>
       </c>
-      <c r="E33" s="23">
-        <v>1</v>
-      </c>
-      <c r="F33" s="23"/>
-      <c r="G33" s="25"/>
-      <c r="H33" s="23"/>
-      <c r="I33" s="23"/>
-      <c r="J33" s="23"/>
-      <c r="K33" s="23"/>
-      <c r="L33" s="25"/>
-      <c r="M33" s="25"/>
-      <c r="N33" s="24"/>
-      <c r="O33" s="26"/>
-      <c r="P33" s="23"/>
-      <c r="Q33" s="25"/>
-      <c r="R33" s="23"/>
-      <c r="S33" s="23"/>
-      <c r="T33" s="23"/>
-      <c r="U33" s="23"/>
-      <c r="V33" s="25"/>
-      <c r="W33" s="23"/>
-      <c r="X33" s="23"/>
-      <c r="Y33" s="23"/>
-      <c r="Z33" s="25"/>
-      <c r="AA33" s="25"/>
-      <c r="AB33" s="25"/>
-      <c r="AC33" s="25"/>
-      <c r="AD33" s="25"/>
-      <c r="AE33" s="25"/>
-    </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A34" s="25"/>
-      <c r="B34" s="25"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
-      <c r="I34" s="25"/>
-      <c r="J34" s="25"/>
-      <c r="K34" s="25"/>
-      <c r="L34" s="25"/>
-      <c r="M34" s="25"/>
-      <c r="N34" s="25"/>
-      <c r="O34" s="25"/>
-      <c r="P34" s="25"/>
-      <c r="Q34" s="25"/>
-      <c r="R34" s="25"/>
-      <c r="S34" s="25"/>
-      <c r="T34" s="25"/>
-      <c r="U34" s="25"/>
-      <c r="V34" s="25"/>
-      <c r="W34" s="25"/>
-      <c r="X34" s="25"/>
-      <c r="Y34" s="25"/>
-      <c r="Z34" s="25"/>
-      <c r="AA34" s="25"/>
-      <c r="AB34" s="25"/>
-      <c r="AC34" s="25"/>
-      <c r="AD34" s="25"/>
-      <c r="AE34" s="25"/>
-    </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A35" s="25"/>
-      <c r="B35" s="25"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="25"/>
-      <c r="I35" s="25"/>
-      <c r="J35" s="25"/>
-      <c r="K35" s="25"/>
-      <c r="L35" s="25"/>
-      <c r="M35" s="25"/>
-      <c r="N35" s="25"/>
-      <c r="O35" s="25"/>
-      <c r="P35" s="25"/>
-      <c r="Q35" s="25"/>
-      <c r="R35" s="25"/>
-      <c r="S35" s="25"/>
-      <c r="T35" s="25"/>
-      <c r="U35" s="25"/>
-      <c r="V35" s="25"/>
-      <c r="W35" s="25"/>
-      <c r="X35" s="25"/>
-      <c r="Y35" s="25"/>
-      <c r="Z35" s="25"/>
-      <c r="AA35" s="25"/>
-      <c r="AB35" s="25"/>
-      <c r="AC35" s="25"/>
-      <c r="AD35" s="25"/>
-      <c r="AE35" s="25"/>
-    </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A36" s="25"/>
-      <c r="B36" s="25"/>
-      <c r="C36" s="25"/>
-      <c r="D36" s="25"/>
-      <c r="E36" s="25"/>
-      <c r="F36" s="25"/>
-      <c r="G36" s="25"/>
-      <c r="H36" s="25"/>
-      <c r="I36" s="25"/>
-      <c r="J36" s="25"/>
-      <c r="K36" s="25"/>
-      <c r="L36" s="25"/>
-      <c r="M36" s="25"/>
-      <c r="N36" s="25"/>
-      <c r="O36" s="25"/>
-      <c r="P36" s="25"/>
-      <c r="Q36" s="25"/>
-      <c r="R36" s="25"/>
-      <c r="S36" s="25"/>
-      <c r="T36" s="25"/>
-      <c r="U36" s="25"/>
-      <c r="V36" s="25"/>
-      <c r="W36" s="25"/>
-      <c r="X36" s="25"/>
-      <c r="Y36" s="25"/>
-      <c r="Z36" s="25"/>
-      <c r="AA36" s="25"/>
-      <c r="AB36" s="25"/>
-      <c r="AC36" s="25"/>
-      <c r="AD36" s="25"/>
-      <c r="AE36" s="25"/>
-    </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A37" s="25"/>
-      <c r="B37" s="25"/>
-      <c r="C37" s="25"/>
-      <c r="D37" s="25"/>
-      <c r="E37" s="25"/>
-      <c r="F37" s="25"/>
-      <c r="G37" s="25"/>
-      <c r="H37" s="25"/>
-      <c r="I37" s="25"/>
-      <c r="J37" s="25"/>
-      <c r="K37" s="25"/>
-      <c r="L37" s="25"/>
-      <c r="M37" s="25"/>
-      <c r="N37" s="25"/>
-      <c r="O37" s="25"/>
-      <c r="P37" s="25"/>
-      <c r="Q37" s="25"/>
-      <c r="R37" s="25"/>
-      <c r="S37" s="25"/>
-      <c r="T37" s="25"/>
-      <c r="U37" s="25"/>
-      <c r="V37" s="25"/>
-      <c r="W37" s="25"/>
-      <c r="X37" s="25"/>
-      <c r="Y37" s="25"/>
-      <c r="Z37" s="25"/>
-      <c r="AA37" s="25"/>
-      <c r="AB37" s="25"/>
-      <c r="AC37" s="25"/>
-      <c r="AD37" s="25"/>
-      <c r="AE37" s="25"/>
+      <c r="E33" s="5">
+        <v>20251110309</v>
+      </c>
+      <c r="F33" s="7">
+        <v>1</v>
+      </c>
+      <c r="G33" s="7"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="7"/>
+      <c r="L33" s="7"/>
+      <c r="M33" s="22"/>
+      <c r="N33" s="22"/>
+      <c r="O33" s="8"/>
+      <c r="P33" s="22"/>
+      <c r="Q33" s="7"/>
+      <c r="R33" s="22"/>
+      <c r="S33" s="7"/>
+      <c r="T33" s="7"/>
+      <c r="U33" s="7"/>
+      <c r="V33" s="7"/>
+      <c r="W33" s="22"/>
+      <c r="X33" s="7"/>
+      <c r="Y33" s="7"/>
+      <c r="Z33" s="7"/>
+      <c r="AA33" s="22"/>
+      <c r="AB33" s="22"/>
+      <c r="AC33" s="22"/>
+      <c r="AD33" s="22"/>
+      <c r="AE33" s="22"/>
+      <c r="AF33" s="22"/>
+    </row>
+    <row r="34" spans="1:32" x14ac:dyDescent="0.15">
+      <c r="A34" s="22"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="I34" s="22"/>
+      <c r="J34" s="22"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
+      <c r="M34" s="22"/>
+      <c r="N34" s="22"/>
+      <c r="O34" s="22"/>
+      <c r="P34" s="22"/>
+      <c r="Q34" s="22"/>
+      <c r="R34" s="22"/>
+      <c r="S34" s="22"/>
+      <c r="T34" s="22"/>
+      <c r="U34" s="22"/>
+      <c r="V34" s="22"/>
+      <c r="W34" s="22"/>
+      <c r="X34" s="22"/>
+      <c r="Y34" s="22"/>
+      <c r="Z34" s="22"/>
+      <c r="AA34" s="22"/>
+      <c r="AB34" s="22"/>
+      <c r="AC34" s="22"/>
+      <c r="AD34" s="22"/>
+      <c r="AE34" s="22"/>
+      <c r="AF34" s="22"/>
+    </row>
+    <row r="35" spans="1:32" x14ac:dyDescent="0.15">
+      <c r="A35" s="22"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+      <c r="I35" s="22"/>
+      <c r="J35" s="22"/>
+      <c r="K35" s="22"/>
+      <c r="L35" s="22"/>
+      <c r="M35" s="22"/>
+      <c r="N35" s="22"/>
+      <c r="O35" s="22"/>
+      <c r="P35" s="22"/>
+      <c r="Q35" s="22"/>
+      <c r="R35" s="22"/>
+      <c r="S35" s="22"/>
+      <c r="T35" s="22"/>
+      <c r="U35" s="22"/>
+      <c r="V35" s="22"/>
+      <c r="W35" s="22"/>
+      <c r="X35" s="22"/>
+      <c r="Y35" s="22"/>
+      <c r="Z35" s="22"/>
+      <c r="AA35" s="22"/>
+      <c r="AB35" s="22"/>
+      <c r="AC35" s="22"/>
+      <c r="AD35" s="22"/>
+      <c r="AE35" s="22"/>
+      <c r="AF35" s="22"/>
+    </row>
+    <row r="36" spans="1:32" x14ac:dyDescent="0.15">
+      <c r="A36" s="22"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="22"/>
+      <c r="H36" s="22"/>
+      <c r="I36" s="22"/>
+      <c r="J36" s="22"/>
+      <c r="K36" s="22"/>
+      <c r="L36" s="22"/>
+      <c r="M36" s="22"/>
+      <c r="N36" s="22"/>
+      <c r="O36" s="22"/>
+      <c r="P36" s="22"/>
+      <c r="Q36" s="22"/>
+      <c r="R36" s="22"/>
+      <c r="S36" s="22"/>
+      <c r="T36" s="22"/>
+      <c r="U36" s="22"/>
+      <c r="V36" s="22"/>
+      <c r="W36" s="22"/>
+      <c r="X36" s="22"/>
+      <c r="Y36" s="22"/>
+      <c r="Z36" s="22"/>
+      <c r="AA36" s="22"/>
+      <c r="AB36" s="22"/>
+      <c r="AC36" s="22"/>
+      <c r="AD36" s="22"/>
+      <c r="AE36" s="22"/>
+      <c r="AF36" s="22"/>
+    </row>
+    <row r="37" spans="1:32" x14ac:dyDescent="0.15">
+      <c r="A37" s="22"/>
+      <c r="B37" s="22"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="22"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="22"/>
+      <c r="M37" s="22"/>
+      <c r="N37" s="22"/>
+      <c r="O37" s="22"/>
+      <c r="P37" s="22"/>
+      <c r="Q37" s="22"/>
+      <c r="R37" s="22"/>
+      <c r="S37" s="22"/>
+      <c r="T37" s="22"/>
+      <c r="U37" s="22"/>
+      <c r="V37" s="22"/>
+      <c r="W37" s="22"/>
+      <c r="X37" s="22"/>
+      <c r="Y37" s="22"/>
+      <c r="Z37" s="22"/>
+      <c r="AA37" s="22"/>
+      <c r="AB37" s="22"/>
+      <c r="AC37" s="22"/>
+      <c r="AD37" s="22"/>
+      <c r="AE37" s="22"/>
+      <c r="AF37" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="AA5:AB5"/>
-    <mergeCell ref="Q5:R5"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="U5:V5"/>
-    <mergeCell ref="W5:X5"/>
-    <mergeCell ref="Y5:Z5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="O5:P5"/>
+  <mergeCells count="17">
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="AB5:AC5"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="V5:W5"/>
+    <mergeCell ref="X5:Y5"/>
+    <mergeCell ref="Z5:AA5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Datos Tesis Upstream/Algoritmos y Programacion/2526-1/Participación Algoritmos 2526-1.xlsx
+++ b/Datos Tesis Upstream/Algoritmos y Programacion/2526-1/Participación Algoritmos 2526-1.xlsx
@@ -16,6 +16,7 @@
     <sheet name="Partic" sheetId="1" r:id="rId1"/>
     <sheet name="Total" sheetId="2" r:id="rId2"/>
     <sheet name="Estandar" sheetId="3" r:id="rId3"/>
+    <sheet name="Cronograma" sheetId="4" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -6809,4 +6810,360 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">semana</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dia_sesion</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tema</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tipo_sesion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>4</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">repaso</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>5</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>5</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>6</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>6</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>7</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sin_clase</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>7</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>8</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>8</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>9</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>9</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>10</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>10</v>
+      </c>
+      <c r="B21">
+        <v>2</v>
+      </c>
+      <c r="C21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>11</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>11</v>
+      </c>
+      <c r="B23">
+        <v>2</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>12</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">administrativa</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>12</v>
+      </c>
+      <c r="B25">
+        <v>2</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">administrativa</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nota:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tema = código del catálogo de la asignatura. Si la sesión no cubre contenido nuevo: tema = 0 y tipo_sesion indica la causa (evaluacion, repaso, sin_clase, administrativa). Si tema &gt; 0 la sesión es de contenido y tipo_sesion queda vacío.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>